--- a/data/2026/10/pedidos_2026-10-22.xlsx
+++ b/data/2026/10/pedidos_2026-10-22.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0014532D"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBF7D0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,913 +433,908 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nombre de contacto</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Telefono</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Municipio</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Direccion destinatario</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Punto de referencia</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Producto / Quien recibe</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Monto a cobrar (COD)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Ya pagado (Si=Estandar / No=COD)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Peso (Lbs)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Fecha de entrega</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Indicaciones para entrega</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Numero de emergencia</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Estado subida</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Error</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>observations</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>vat</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_number</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>apellido</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>apellido2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>apellido_destino</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>lugar_nacimiento</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. rosa</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
+          <t>rosa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>70594866</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Por la nevería del mercado de San Rafael Cedros</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Cuscatlán</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>SAN RAFAEL CEDROS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Por la nevería del mercado de San Rafael Cedros</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Rose gold MINI</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2. Walter González</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Walter González</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>78653477</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Metrocentro</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>lugar de trabajo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Sonsonate</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>SONSONATE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Metrocentro</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>lugar de trabajo</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>MRW-200H Full Negro + Regalía</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3. Saul Fernando Córdova</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Saul Fernando Córdova</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>76882668</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>El coyolito</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(en Agroservicio La Campiña)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Chalatenango</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>TEJUTLA</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>El coyolito</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(en Agroservicio La Campiña)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Casio World + Regalía</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4. Marisela valles</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Marisela valles</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>70611492</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cantón el tablón</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Punto de referencia cruz de calle el tablón</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Usulután</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>SAN FRANCISCO JAVIER</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Cantón el tablón</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Punto de referencia cruz de calle el tablón</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Casio F-105 mas regalia</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5. Eduardo salazar melendez</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Eduardo salazar melendez</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>76316154</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Plaza Centro • Cara Sucia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>referencia, frente a banco de fomento</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Ahuachapán</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>AHUACHAPAN</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Plaza Centro • Cara Sucia</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>referencia, frente a banco de fomento</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>casio world</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6. Aracely Guadalupe Martínez</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Aracely Guadalupe Martínez</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>76124498</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Col. Las delicias pasaje #2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>por Estadio Sergio Torres</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Usulután</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>USULUTAN</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Col. Las delicias pasaje #2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> por Estadio Sergio Torres</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Casio old money rose gold</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7. Roxana Servano Alvarado</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Roxana Servano Alvarado</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>70026649</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Metrocentro lourdes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>es Dirección del trabajo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>La Libertad</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>COLON</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Metrocentro lourdes </t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>es Dirección del trabajo</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Casio rose gold diamond</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>a las 2pm tiene libre para recibir</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8. CORNEJO MORAN</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
+          <t>CORNEJO MORAN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>74162337</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Autopista Sur km 63 y medio</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Universidad Autónoma deSANTA ANA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Santa Ana</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>SANTA ANA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autopista Sur km 63 y medio </t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Universidad Autónoma deSANTA ANA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>wood cafe y aviador negro</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9. jaime walter</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
+          <t>jaime walter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>62888393</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nueva san miguel</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>residencial nueva san miguel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>San Miguel</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>SAN MIGUEL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Nueva san miguel</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>residencial nueva san miguel</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Seiko 5 fondo verde</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10. Karla Fabiola Figueroa Sibrián</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Karla Fabiola Figueroa Sibrián</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>63083979</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Final 13 Avenida Sur, N° 1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entrega en portón de Maternidad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Santa Ana</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>SANTA ANA</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Final 13 Avenida Sur, N° 1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Entrega en portón de Maternidad</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Casio old money rose gold</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11. Yanci Maricela Lemus</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Yanci Maricela Lemus</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>72652826</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1ra Ave. Norte #220 Colonia las brisas, Nueva Concepción Chalatenango centro</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>referencia: en una clínica dental, que se llama Dentalblue</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Chalatenango</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>NUEVA CONCEPCION</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1ra Ave. Norte #220 Colonia las brisas, Nueva Concepción Chalatenango centro</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>referencia: en una clínica dental, que se llama Dentalblue</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Casio old money rose gold</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12. Blanca Estela Vasquez de Flores</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Blanca Estela Vasquez de Flores</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>78369073</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Residencial El Calvario</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pasaje 1 casa 5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Usulután</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>USULUTAN</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Residencial El Calvario</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> pasaje 1 casa 5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Seiko 5 dorado</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Contactar al cliente para coordinar la entrega</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Karla Areli Gámez Rodríguez</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>62859358</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Km 3 carretera a planes de renderos</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>casa 1 | 13.661799, -89.201431</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PANCHIMALCO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Casio rosegold diamond</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>entregar lunes por la tarde</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
